--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Long Term Wealth Enhancement Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Long Term Wealth Enhancement Fund.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BBA991-3314-4160-9A10-E97A456827B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CB8837-B42A-45F1-ADD8-824C9753BDD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Long Term Wealth Enhancement Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -67,6 +67,15 @@
     <t>Listed / Awaiting Listing On Stock Exchanges</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>TVS Motor Company Ltd.</t>
   </si>
   <si>
@@ -76,13 +85,10 @@
     <t>Automobiles</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A01034</t>
   </si>
   <si>
     <t>Maruti Suzuki India Ltd.</t>
@@ -91,10 +97,40 @@
     <t>INE585B01010</t>
   </si>
   <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A01034</t>
+    <t>The Ethos Ltd.</t>
+  </si>
+  <si>
+    <t>INE04TZ01018</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Avenue Supermarts Ltd.</t>
+  </si>
+  <si>
+    <t>INE192R01011</t>
+  </si>
+  <si>
+    <t>Retailing</t>
+  </si>
+  <si>
+    <t>Sun Pharmaceutical Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals &amp; Biotechnology</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
   </si>
   <si>
     <t>Red Tape Ltd</t>
@@ -103,16 +139,106 @@
     <t>INE0LXT01019</t>
   </si>
   <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Sun Pharmaceutical Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE044A01036</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals &amp; Biotechnology</t>
+    <t>Zomato Ltd.</t>
+  </si>
+  <si>
+    <t>INE758T01015</t>
+  </si>
+  <si>
+    <t>Reliance Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE002A01018</t>
+  </si>
+  <si>
+    <t>Petroleum Products</t>
+  </si>
+  <si>
+    <t>State Bank Of India</t>
+  </si>
+  <si>
+    <t>INE062A01020</t>
+  </si>
+  <si>
+    <t>Infosys Ltd.</t>
+  </si>
+  <si>
+    <t>INE009A01021</t>
+  </si>
+  <si>
+    <t>It - Software</t>
+  </si>
+  <si>
+    <t>RR Kabel Ltd.</t>
+  </si>
+  <si>
+    <t>INE777K01022</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>HCL Technologies Ltd.</t>
+  </si>
+  <si>
+    <t>INE860A01027</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Britannia Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE216A01030</t>
+  </si>
+  <si>
+    <t>Food Products</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>Trent Ltd.</t>
@@ -121,132 +247,6 @@
     <t>INE849A01020</t>
   </si>
   <si>
-    <t>Retailing</t>
-  </si>
-  <si>
-    <t>Avenue Supermarts Ltd.</t>
-  </si>
-  <si>
-    <t>INE192R01011</t>
-  </si>
-  <si>
-    <t>The Ethos Ltd.</t>
-  </si>
-  <si>
-    <t>INE04TZ01018</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
-  </si>
-  <si>
-    <t>State Bank Of India</t>
-  </si>
-  <si>
-    <t>INE062A01020</t>
-  </si>
-  <si>
-    <t>Zomato Ltd.</t>
-  </si>
-  <si>
-    <t>INE758T01015</t>
-  </si>
-  <si>
-    <t>Reliance Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE002A01018</t>
-  </si>
-  <si>
-    <t>Petroleum Products</t>
-  </si>
-  <si>
-    <t>HCL Technologies Ltd.</t>
-  </si>
-  <si>
-    <t>INE860A01027</t>
-  </si>
-  <si>
-    <t>It - Software</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Infosys Ltd.</t>
-  </si>
-  <si>
-    <t>INE009A01021</t>
-  </si>
-  <si>
-    <t>Tata Consultancy Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE467B01029</t>
-  </si>
-  <si>
-    <t>Britannia Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE216A01030</t>
-  </si>
-  <si>
-    <t>Food Products</t>
-  </si>
-  <si>
-    <t>360 One Wam Ltd.</t>
-  </si>
-  <si>
-    <t>INE466L01038</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>RR Kabel Ltd.</t>
-  </si>
-  <si>
-    <t>INE777K01022</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
     <t>Thirumalai Chemicals Ltd</t>
   </si>
   <si>
@@ -313,7 +313,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -325,7 +325,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - Nifty 500 TRI</t>
+    <t xml:space="preserve">Benchmark name - Nifty 500 TRI </t>
   </si>
 </sst>
 </file>
@@ -1137,10 +1137,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>3810.7700000000004</v>
+        <v>3824.3800000000006</v>
       </c>
       <c r="H5" s="13">
-        <v>0.99286163527850002</v>
+        <v>0.95988676962310004</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1174,10 +1174,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>3810.7700000000004</v>
+        <v>3824.3800000000006</v>
       </c>
       <c r="H7" s="13">
-        <v>0.99286163527850002</v>
+        <v>0.95988676962310004</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1200,13 +1200,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>16342</v>
+        <v>26468</v>
       </c>
       <c r="G8" s="18">
-        <v>401.67</v>
+        <v>382.67</v>
       </c>
       <c r="H8" s="19">
-        <v>0.10465148330720001</v>
+        <v>9.6046906984099997E-2</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1229,13 +1229,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="17">
-        <v>30911</v>
+        <v>13508</v>
       </c>
       <c r="G9" s="18">
-        <v>387.25</v>
+        <v>375.63</v>
       </c>
       <c r="H9" s="19">
-        <v>0.100894482811</v>
+        <v>9.4279927013999995E-2</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1258,13 +1258,13 @@
         <v>17</v>
       </c>
       <c r="F10" s="17">
-        <v>2736</v>
+        <v>18725</v>
       </c>
       <c r="G10" s="18">
-        <v>336.82</v>
+        <v>364.18</v>
       </c>
       <c r="H10" s="19">
-        <v>8.77554027125E-2</v>
+        <v>9.1406074647799998E-2</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1287,13 +1287,13 @@
         <v>20</v>
       </c>
       <c r="F11" s="17">
-        <v>18725</v>
+        <v>2736</v>
       </c>
       <c r="G11" s="18">
-        <v>318.08999999999997</v>
+        <v>337.05</v>
       </c>
       <c r="H11" s="19">
-        <v>8.2875470722700004E-2</v>
+        <v>8.4596675984500005E-2</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1316,13 +1316,13 @@
         <v>27</v>
       </c>
       <c r="F12" s="17">
-        <v>33714</v>
+        <v>7458</v>
       </c>
       <c r="G12" s="18">
-        <v>227.52</v>
+        <v>212.51</v>
       </c>
       <c r="H12" s="19">
-        <v>5.9278276899100001E-2</v>
+        <v>5.33381979334E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1345,13 +1345,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="17">
-        <v>11884</v>
+        <v>5147</v>
       </c>
       <c r="G13" s="18">
-        <v>207.25</v>
+        <v>205.99</v>
       </c>
       <c r="H13" s="19">
-        <v>5.3997111846599999E-2</v>
+        <v>5.1701733529299999E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1374,13 +1374,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="17">
-        <v>3392</v>
+        <v>11884</v>
       </c>
       <c r="G14" s="18">
-        <v>195.15</v>
+        <v>199.37</v>
       </c>
       <c r="H14" s="19">
-        <v>5.08445663539E-2</v>
+        <v>5.0040169977800003E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1400,16 +1400,16 @@
         <v>13</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F15" s="17">
-        <v>5147</v>
+        <v>9920</v>
       </c>
       <c r="G15" s="18">
-        <v>188.62</v>
+        <v>184.14</v>
       </c>
       <c r="H15" s="19">
-        <v>4.9143233951699998E-2</v>
+        <v>4.6217569843600002E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>13</v>
@@ -1432,13 +1432,13 @@
         <v>27</v>
       </c>
       <c r="F16" s="17">
-        <v>7458</v>
+        <v>134856</v>
       </c>
       <c r="G16" s="18">
-        <v>181.33</v>
+        <v>180.91</v>
       </c>
       <c r="H16" s="19">
-        <v>4.7243890427699997E-2</v>
+        <v>4.5406867385700003E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1449,25 +1449,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F17" s="17">
-        <v>9920</v>
+        <v>65080</v>
       </c>
       <c r="G17" s="18">
-        <v>161.33000000000001</v>
+        <v>155.09</v>
       </c>
       <c r="H17" s="19">
-        <v>4.2033071431599997E-2</v>
+        <v>3.8926267552099998E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1487,16 +1487,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F18" s="17">
-        <v>18854</v>
+        <v>10846</v>
       </c>
       <c r="G18" s="18">
-        <v>145.72</v>
+        <v>154.11000000000001</v>
       </c>
       <c r="H18" s="19">
-        <v>3.7966027205200002E-2</v>
+        <v>3.8680295908500001E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1507,25 +1507,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F19" s="17">
-        <v>65080</v>
+        <v>18854</v>
       </c>
       <c r="G19" s="18">
-        <v>143.4</v>
+        <v>153.15</v>
       </c>
       <c r="H19" s="19">
-        <v>3.73615722017E-2</v>
+        <v>3.8439344094400002E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1536,25 +1536,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F20" s="17">
-        <v>10846</v>
+        <v>7889</v>
       </c>
       <c r="G20" s="18">
-        <v>137.21</v>
+        <v>123.28</v>
       </c>
       <c r="H20" s="19">
-        <v>3.57488237224E-2</v>
+        <v>3.0942228794999999E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1565,25 +1565,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F21" s="17">
-        <v>6544</v>
+        <v>8132</v>
       </c>
       <c r="G21" s="18">
-        <v>112.91</v>
+        <v>115.94</v>
       </c>
       <c r="H21" s="19">
-        <v>2.9417678642200001E-2</v>
+        <v>2.9099951382999999E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1594,25 +1594,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F22" s="17">
-        <v>14424</v>
+        <v>6544</v>
       </c>
       <c r="G22" s="18">
-        <v>107.7</v>
+        <v>107.1</v>
       </c>
       <c r="H22" s="19">
-        <v>2.8060260293699998E-2</v>
+        <v>2.68811867614E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -1632,16 +1632,16 @@
         <v>13</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F23" s="17">
-        <v>5000</v>
+        <v>14424</v>
       </c>
       <c r="G23" s="18">
-        <v>93.99</v>
+        <v>93.26</v>
       </c>
       <c r="H23" s="19">
-        <v>2.44882438719E-2</v>
+        <v>2.3407464774700001E-2</v>
       </c>
       <c r="I23" s="18" t="s">
         <v>13</v>
@@ -1652,25 +1652,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F24" s="17">
-        <v>2056</v>
+        <v>1523</v>
       </c>
       <c r="G24" s="18">
-        <v>84.55</v>
+        <v>81.180000000000007</v>
       </c>
       <c r="H24" s="19">
-        <v>2.20287373058E-2</v>
+        <v>2.0375487780499999E-2</v>
       </c>
       <c r="I24" s="18" t="s">
         <v>13</v>
@@ -1681,25 +1681,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="F25" s="17">
-        <v>1337</v>
+        <v>6634</v>
       </c>
       <c r="G25" s="18">
-        <v>68.58</v>
+        <v>79.09</v>
       </c>
       <c r="H25" s="19">
-        <v>1.78678983374E-2</v>
+        <v>1.9850915601799999E-2</v>
       </c>
       <c r="I25" s="18" t="s">
         <v>13</v>
@@ -1710,25 +1710,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F26" s="17">
-        <v>6514</v>
+        <v>1337</v>
       </c>
       <c r="G26" s="18">
-        <v>65.64</v>
+        <v>73.680000000000007</v>
       </c>
       <c r="H26" s="19">
-        <v>1.7101907945000001E-2</v>
+        <v>1.8493051732800001E-2</v>
       </c>
       <c r="I26" s="18" t="s">
         <v>13</v>
@@ -1739,25 +1739,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D27" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F27" s="17">
-        <v>6634</v>
+        <v>2056</v>
       </c>
       <c r="G27" s="18">
-        <v>65.42</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="H27" s="19">
-        <v>1.7044588935999999E-2</v>
+        <v>1.7873102794399999E-2</v>
       </c>
       <c r="I27" s="18" t="s">
         <v>13</v>
@@ -1768,25 +1768,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F28" s="17">
-        <v>107486</v>
+        <v>6514</v>
       </c>
       <c r="G28" s="18">
-        <v>60.33</v>
+        <v>64.97</v>
       </c>
       <c r="H28" s="19">
-        <v>1.5718435501500001E-2</v>
+        <v>1.6306916002700001E-2</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>13</v>
@@ -1797,25 +1797,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F29" s="17">
-        <v>970</v>
+        <v>107486</v>
       </c>
       <c r="G29" s="18">
-        <v>41.95</v>
+        <v>62.21</v>
       </c>
       <c r="H29" s="19">
-        <v>1.0929692844199999E-2</v>
+        <v>1.56141795371E-2</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>13</v>
@@ -1826,25 +1826,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D30" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="F30" s="17">
-        <v>3338</v>
+        <v>732</v>
       </c>
       <c r="G30" s="18">
-        <v>40.92</v>
+        <v>41.31</v>
       </c>
       <c r="H30" s="19">
-        <v>1.0661335665899999E-2</v>
+        <v>1.03684577508E-2</v>
       </c>
       <c r="I30" s="18" t="s">
         <v>13</v>
@@ -1867,13 +1867,13 @@
         <v>77</v>
       </c>
       <c r="F31" s="17">
-        <v>15694</v>
+        <v>2542</v>
       </c>
       <c r="G31" s="18">
-        <v>37.42</v>
+        <v>6.35</v>
       </c>
       <c r="H31" s="19">
-        <v>9.7494423416000005E-3</v>
+        <v>1.5937958537000001E-3</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>13</v>
@@ -2388,10 +2388,10 @@
         <v>13</v>
       </c>
       <c r="G59" s="12">
-        <v>56.87</v>
+        <v>160.62</v>
       </c>
       <c r="H59" s="13">
-        <v>1.48169638152E-2</v>
+        <v>4.0314250397900001E-2</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>13</v>
@@ -2425,10 +2425,10 @@
         <v>13</v>
       </c>
       <c r="G61" s="21">
-        <v>-29.471755209999174</v>
+        <v>-0.80090379000012035</v>
       </c>
       <c r="H61" s="22">
-        <v>-7.6785990947647164E-3</v>
+        <v>-2.0102002200692888E-4</v>
       </c>
       <c r="I61" s="21" t="s">
         <v>13</v>
@@ -2454,10 +2454,10 @@
         <v>13</v>
       </c>
       <c r="G62" s="21">
-        <v>3838.1682447899998</v>
+        <v>3984.1990962099999</v>
       </c>
       <c r="H62" s="22">
-        <v>0.99999999999893507</v>
+        <v>0.99999999999899292</v>
       </c>
       <c r="I62" s="21" t="s">
         <v>13</v>
@@ -2532,7 +2532,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="2:2" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B88" s="24" t="s">
         <v>101</v>
       </c>
